--- a/Controlling/Automatisation/alle_bestellungen_pro_shop.xlsx
+++ b/Controlling/Automatisation/alle_bestellungen_pro_shop.xlsx
@@ -44,7 +44,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,13 +52,24 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ADD8E6"/>
+        <bgColor rgb="00ADD8E6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -73,8 +84,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -166,7 +178,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Umsatz pro Monat</a:t>
+              <a:t>Wachstum pro Monat</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -180,7 +192,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B6</f>
+              <f>'Dashboard'!D6</f>
             </strRef>
           </tx>
           <spPr>
@@ -203,7 +215,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$7:$B$8</f>
+              <f>'Dashboard'!$D$7:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -329,7 +341,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>14</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>5</row>
       <rowOff>0</rowOff>
@@ -353,7 +365,7 @@
     <from>
       <col>10</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="5040000"/>
@@ -665,49 +677,60 @@
   </sheetPr>
   <dimension ref="A1:I578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -18613,49 +18636,60 @@
   </sheetPr>
   <dimension ref="A1:I263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -26796,49 +26830,60 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -26888,49 +26933,60 @@
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -27042,49 +27098,60 @@
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -27165,49 +27232,60 @@
   </sheetPr>
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -27815,49 +27893,60 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -27907,49 +27996,60 @@
   </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -28185,49 +28285,60 @@
   </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -28401,49 +28512,60 @@
   </sheetPr>
   <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -29144,49 +29266,60 @@
   </sheetPr>
   <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -30135,49 +30268,60 @@
   </sheetPr>
   <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -31095,49 +31239,60 @@
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -31218,49 +31373,60 @@
   </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -31434,49 +31600,60 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -31681,49 +31858,60 @@
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -31866,49 +32054,60 @@
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -32051,49 +32250,60 @@
   </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -32329,49 +32539,60 @@
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -32452,24 +32673,30 @@
   </sheetPr>
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Monat</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Bestellungen</t>
         </is>
@@ -33154,13 +33381,20 @@
   </sheetPr>
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
+      <c r="B1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33168,7 +33402,7 @@
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>20064</v>
       </c>
     </row>
@@ -33188,7 +33422,7 @@
           <t>Ø Bestellwert</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>82.23</v>
       </c>
     </row>
@@ -33203,7 +33437,7 @@
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Wachstum Monat %</t>
         </is>
@@ -33219,7 +33453,7 @@
       <c r="B7" t="n">
         <v>16369</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33232,17 +33466,17 @@
       <c r="B8" t="n">
         <v>3695</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>-77.4268434235445</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Top Produkte</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
@@ -33254,22 +33488,22 @@
           <t>Unbekannt</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>141722</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Region/Shop</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>Anzahl Gutscheine</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
@@ -33284,7 +33518,7 @@
       <c r="B24" t="n">
         <v>29</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>1368</v>
       </c>
     </row>
@@ -33297,7 +33531,7 @@
       <c r="B25" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -33310,7 +33544,7 @@
       <c r="B26" t="n">
         <v>107</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>2910</v>
       </c>
     </row>
@@ -33323,7 +33557,7 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -33336,7 +33570,7 @@
       <c r="B28" t="n">
         <v>43</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>1110</v>
       </c>
     </row>
@@ -33349,7 +33583,7 @@
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -33362,7 +33596,7 @@
       <c r="B30" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>150</v>
       </c>
     </row>
@@ -33375,7 +33609,7 @@
       <c r="B31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>154</v>
       </c>
     </row>
@@ -33388,7 +33622,7 @@
       <c r="B32" t="n">
         <v>262</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>10075</v>
       </c>
     </row>
@@ -33401,7 +33635,7 @@
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -33414,7 +33648,7 @@
       <c r="B34" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>40</v>
       </c>
     </row>
@@ -33427,7 +33661,7 @@
       <c r="B35" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -33440,7 +33674,7 @@
       <c r="B36" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>785</v>
       </c>
     </row>
@@ -33453,7 +33687,7 @@
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -33466,7 +33700,7 @@
       <c r="B38" t="n">
         <v>7</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>215</v>
       </c>
     </row>
@@ -33479,7 +33713,7 @@
       <c r="B39" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>180</v>
       </c>
     </row>
@@ -33492,7 +33726,7 @@
       <c r="B40" t="n">
         <v>22</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>940</v>
       </c>
     </row>
@@ -33505,7 +33739,7 @@
       <c r="B41" t="n">
         <v>30</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -33518,7 +33752,7 @@
       <c r="B42" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>75</v>
       </c>
     </row>
@@ -33531,7 +33765,7 @@
       <c r="B43" t="n">
         <v>5</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>207</v>
       </c>
     </row>
@@ -33544,7 +33778,7 @@
       <c r="B44" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -33557,7 +33791,7 @@
       <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -33570,7 +33804,7 @@
       <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>200</v>
       </c>
     </row>
@@ -33583,7 +33817,7 @@
       <c r="B47" t="n">
         <v>7</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>185</v>
       </c>
     </row>
@@ -33596,7 +33830,7 @@
       <c r="B48" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -33614,49 +33848,60 @@
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -33737,49 +33982,60 @@
   </sheetPr>
   <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -37115,49 +37371,60 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -37207,49 +37474,60 @@
   </sheetPr>
   <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -38601,49 +38879,60 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -38693,49 +38982,60 @@
   </sheetPr>
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
@@ -39002,49 +39302,60 @@
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gutschein Code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Produktname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Privatkauf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Auftraggeber</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>

--- a/Controlling/Automatisation/alle_bestellungen_pro_shop.xlsx
+++ b/Controlling/Automatisation/alle_bestellungen_pro_shop.xlsx
@@ -40,30 +40,30 @@
     <sheet name="WunCard" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$C$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alle Shops'!$A$1:$H$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$C$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alle Shops'!$A$1:$H$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'0711Card'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AbensbergCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Baden-Baden-Card'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bad Waldsee CityCard'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BalingenCard'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bad Waldsee CityCard'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BalingenCard'!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BesigheimCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SchwabachCard'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CalwCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'DETTINGEN ERMSCARD'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ECHT FREIBURG CARD'!$A$1:$H$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ECHT FREIBURG CARD'!$A$1:$H$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'EttenheimCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Erlebnisregion Europa-Park-Card'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'FördeCard'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'FördeCard'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'HaslachCard'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'HerbolzheimCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'HU-SmartCard'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'KenzingenCard'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'LahrCard'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'LandshutCard'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'KenzingenCard'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'LahrCard'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'LandshutCard'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'LE-Card'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'NeubulachCard'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'NeuriedCard'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'NeuriedCard'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'PfulbenCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'RatingenCard'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'SRCARD'!$A$1:$H$1</definedName>
@@ -264,7 +264,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!L38</f>
+              <f>'Dashboard'!L42</f>
             </strRef>
           </tx>
           <spPr>
@@ -282,12 +282,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$K$39</f>
+              <f>'Dashboard'!$K$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$L$39</f>
+              <f>'Dashboard'!$L$43</f>
             </numRef>
           </val>
         </ser>
@@ -384,7 +384,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!N38</f>
+              <f>'Dashboard'!N42</f>
             </strRef>
           </tx>
           <spPr>
@@ -394,12 +394,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$M$39:$M$50</f>
+              <f>'Dashboard'!$M$43:$M$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$N$39:$N$50</f>
+              <f>'Dashboard'!$N$43:$N$56</f>
             </numRef>
           </val>
         </ser>
@@ -497,7 +497,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="5040000"/>
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3235</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="6">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>295</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2065</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="13">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -995,14 +995,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LahrCard</t>
+          <t>KenzingenCard</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -1013,14 +1013,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LandshutCard</t>
+          <t>LahrCard</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SchwabachCard</t>
+          <t>LandshutCard</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>75</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -1049,14 +1049,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WunCard</t>
+          <t>NeuriedCard</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
@@ -1067,343 +1067,425 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WürmtalCard</t>
+          <t>SchwabachCard</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>04.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WunCard</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>04.2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WürmtalCard</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Pro Region (Gesamt)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Anzahl Gutscheine</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0711Card</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Bad Waldsee CityCard</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BalingenCard</t>
+          <t>0711Card</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>295</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DETTINGEN ERMSCARD</t>
+          <t>Bad Waldsee CityCard</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ECHT FREIBURG CARD</t>
+          <t>BalingenCard</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>2065</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FördeCard</t>
+          <t>DETTINGEN ERMSCARD</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HaslachCard</t>
+          <t>ECHT FREIBURG CARD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>50</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LahrCard</t>
+          <t>FördeCard</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LandshutCard</t>
+          <t>HaslachCard</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SchwabachCard</t>
+          <t>KenzingenCard</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WunCard</t>
+          <t>LahrCard</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SchwabachCard</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WunCard</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>WürmtalCard</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C39" s="6" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="38">
-      <c r="K38" s="7" t="inlineStr">
+    <row r="42">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>Monat</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="K39" t="inlineStr">
+    <row r="43">
+      <c r="K43" t="inlineStr">
         <is>
           <t>04.2026</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>90</v>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="L43" t="n">
+        <v>173</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>0711Card</t>
         </is>
       </c>
-      <c r="N39" t="n">
+      <c r="N43" t="n">
         <v>250</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Bad Waldsee CityCard</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>BalingenCard</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>DETTINGEN ERMSCARD</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>ECHT FREIBURG CARD</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>2065</v>
       </c>
     </row>
     <row r="44">
       <c r="M44" t="inlineStr">
         <is>
-          <t>FördeCard</t>
+          <t>Bad Waldsee CityCard</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>25</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45">
       <c r="M45" t="inlineStr">
         <is>
-          <t>HaslachCard</t>
+          <t>BalingenCard</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>50</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46">
       <c r="M46" t="inlineStr">
         <is>
-          <t>LahrCard</t>
+          <t>DETTINGEN ERMSCARD</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="M47" t="inlineStr">
         <is>
-          <t>LandshutCard</t>
+          <t>ECHT FREIBURG CARD</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>150</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="48">
       <c r="M48" t="inlineStr">
         <is>
-          <t>SchwabachCard</t>
+          <t>FördeCard</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
       <c r="M49" t="inlineStr">
         <is>
-          <t>WunCard</t>
+          <t>HaslachCard</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="M50" t="inlineStr">
         <is>
+          <t>KenzingenCard</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SchwabachCard</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>WunCard</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="M56" t="inlineStr">
+        <is>
           <t>WürmtalCard</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="N56" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1592,13 +1674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -3699,8 +3781,1844 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>176109983724094</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>18669</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>176106453847462</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>18667</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>176108264981647</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>18665</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>176106197897641</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>18614</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n">
+        <v>176101401396902</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>18612</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>176108057155581</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>40€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>18610</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n">
+        <v>176104437138785</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>60€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>18608</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>176100815385931</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>176103617213962</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>176103666303490</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>176105683128032</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>176108905117262</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>176105256654190</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>176102657446953</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>176107919896861</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>176108078669065</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>176101841280286</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>176108537525064</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
+        <v>176106028483363</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>40€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>18459</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>176101751913967</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>60€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>18444</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n">
+        <v>176100810545752</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>18372</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>176106153010528</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="n">
+        <v>176109936052254</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>176102364358509</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>176102936606153</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>176101155421047</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n">
+        <v>176105366648678</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>176107048552146</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
+        <v>176100288464031</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>176103276720059</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>176109710333425</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>176105318777559</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="n">
+        <v>176107991724890</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>176106258240111</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>176105456917272</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>176102926631179</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>176109646997137</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>176109752157419</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="n">
+        <v>176102805664051</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="n">
+        <v>176109736686764</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="n">
+        <v>176106704735334</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="n">
+        <v>176103994382034</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n">
+        <v>176103077441632</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>176100425441298</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="n">
+        <v>176104184596946</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
+        <v>176108851116987</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="n">
+        <v>176105524080442</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="n">
+        <v>176100598033013</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="n">
+        <v>176105172093051</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="n">
+        <v>176101599944422</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="n">
+        <v>176106134320780</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H58"/>
+  <autoFilter ref="A1:H109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3845,7 +5763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3936,8 +5854,44 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>FördeCard</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>176104920681325</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>27715</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4185,17 +6139,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4240,8 +6194,80 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>KenzingenCard</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>176108852512465</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>100€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>6723</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>KenzingenCard</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>176103786180489</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6723</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4252,7 +6278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7547,8 +9573,2996 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>176100205524388</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>176107270615249</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>176109033123594</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>176105951467179</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>176104441965868</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="n">
+        <v>176105894744023</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="n">
+        <v>176100379152164</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="n">
+        <v>176103109448829</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="n">
+        <v>176102093491233</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>11824</v>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n">
+        <v>176109983724094</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>18669</v>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>176106453847462</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>18667</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="n">
+        <v>176108264981647</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>18665</v>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
+        <v>176106197897641</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>18614</v>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="n">
+        <v>176101401396902</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>18612</v>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="n">
+        <v>176108057155581</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>40€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>18610</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="n">
+        <v>176104437138785</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>60€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>18608</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="n">
+        <v>176100815385931</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="n">
+        <v>176103617213962</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="n">
+        <v>176103666303490</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>18604</v>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="n">
+        <v>176105683128032</v>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="n">
+        <v>176108905117262</v>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="n">
+        <v>176105256654190</v>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="n">
+        <v>176102657446953</v>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="n">
+        <v>176107919896861</v>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>18598</v>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="n">
+        <v>176108078669065</v>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="n">
+        <v>176101841280286</v>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n">
+        <v>176108537525064</v>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>20€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>18594</v>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="n">
+        <v>176106028483363</v>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>40€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>18459</v>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="n">
+        <v>176101751913967</v>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>60€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>18444</v>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="n">
+        <v>176100810545752</v>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>18372</v>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="n">
+        <v>176106153010528</v>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="n">
+        <v>176109936052254</v>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>176102364358509</v>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="n">
+        <v>176102936606153</v>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>176101155421047</v>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="n">
+        <v>176105366648678</v>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="n">
+        <v>176107048552146</v>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="n">
+        <v>176100288464031</v>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="n">
+        <v>176103276720059</v>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="n">
+        <v>176109710333425</v>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="n">
+        <v>176105318777559</v>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="n">
+        <v>176107991724890</v>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="n">
+        <v>176106258240111</v>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="n">
+        <v>176105456917272</v>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>176102926631179</v>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="n">
+        <v>176109646997137</v>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="n">
+        <v>176109752157419</v>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="n">
+        <v>176102805664051</v>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="n">
+        <v>176109736686764</v>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="n">
+        <v>176106704735334</v>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="n">
+        <v>176103994382034</v>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="n">
+        <v>176103077441632</v>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="n">
+        <v>176100425441298</v>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="n">
+        <v>176104184596946</v>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="n">
+        <v>176108851116987</v>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="n">
+        <v>176105524080442</v>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="n">
+        <v>176100598033013</v>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="n">
+        <v>176105172093051</v>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G149" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="n">
+        <v>176101599944422</v>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>ECHT FREIBURG CARD</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="n">
+        <v>176106134320780</v>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein PDF Gutscheinbestellungen Stadtinitiative Freiburg</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>nein, Auftraggeber</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="n">
+        <v>18341</v>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>FördeCard</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="n">
+        <v>176104920681325</v>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="n">
+        <v>27715</v>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>KenzingenCard</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="n">
+        <v>176108852512465</v>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>100€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>6723</v>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>KenzingenCard</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="n">
+        <v>176103786180489</v>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="n">
+        <v>6723</v>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n">
+        <v>176101196338994</v>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>176104766808735</v>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="n">
+        <v>176109693424498</v>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="n">
+        <v>176104088246713</v>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="n">
+        <v>10516</v>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="n">
+        <v>176108785461798</v>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E159" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="n">
+        <v>10516</v>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n">
+        <v>176105696186928</v>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E160" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="n">
+        <v>10514</v>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="n">
+        <v>176102458985928</v>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="n">
+        <v>176108604790385</v>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="n">
+        <v>176107657584448</v>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>5€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>176102959674823</v>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>100€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="n">
+        <v>8617</v>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="n">
+        <v>176109024937531</v>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="n">
+        <v>8614</v>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="n">
+        <v>176109381725578</v>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>5€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="n">
+        <v>8614</v>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="n">
+        <v>176103775527641</v>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>8612</v>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="n">
+        <v>176109703523008</v>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E168" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="n">
+        <v>8610</v>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="n">
+        <v>176107127203231</v>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E169" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="n">
+        <v>8608</v>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n">
+        <v>176104667328262</v>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="n">
+        <v>176108045080305</v>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="n">
+        <v>176108337825284</v>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="n">
+        <v>176108358101011</v>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="n">
+        <v>176100494139997</v>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H91"/>
+  <autoFilter ref="A1:H174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7559,7 +12573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7686,8 +12700,332 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>176101196338994</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>176104766808735</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>176109693424498</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>10519</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>176104088246713</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>10516</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>176108785461798</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>10516</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>176105696186928</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>10514</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>176102458985928</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>176108604790385</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>LahrCard</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>176107657584448</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>5€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>10510</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7698,7 +13036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7825,8 +13163,224 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>176102959674823</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>100€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>8617</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>176109024937531</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>8614</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>176109381725578</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>5€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>8614</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>19.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>176103775527641</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>8612</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>18.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>176109703523008</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>8610</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>LandshutCard</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>176107127203231</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>8608</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7971,17 +13525,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8026,8 +13580,188 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>176104667328262</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>176108045080305</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>176108337825284</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>176108358101011</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>NeuriedCard</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>176100494139997</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>25€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>7628</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8379,7 +14113,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -9068,7 +14802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9195,8 +14929,116 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>176100205524388</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>176107270615249</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Bad Waldsee CityCard</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>176109033123594</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>11803</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9207,7 +15049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9694,8 +15536,224 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>176105951467179</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>176104441965868</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>176105894744023</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>176100379152164</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>176103109448829</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>10€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>11826</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BalingenCard</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>176102093491233</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>50€ Gutschein</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>11824</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
